--- a/Result/profitability/3062.xlsx
+++ b/Result/profitability/3062.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.32</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05500000000000001</v>
+        <v>0.01125000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>6.725</v>
+        <v>6.71125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.33</v>
       </c>
       <c r="M3" t="n">
-        <v>0.09375000000000001</v>
+        <v>0.06000000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>7.678749999999999</v>
+        <v>5.995</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.12</v>
       </c>
       <c r="M4" t="n">
-        <v>0.11625</v>
+        <v>-0.21375</v>
       </c>
       <c r="N4" t="n">
-        <v>6.68625</v>
+        <v>5.945</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.4</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1225</v>
+        <v>-0.10125</v>
       </c>
       <c r="N5" t="n">
-        <v>6.8725</v>
+        <v>6.94125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.35</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.01624999999999999</v>
+        <v>-0.01750000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>7.64625</v>
+        <v>7.64375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.47</v>
       </c>
       <c r="M7" t="n">
-        <v>0.08250000000000002</v>
+        <v>0.14</v>
       </c>
       <c r="N7" t="n">
-        <v>8.775</v>
+        <v>9.123749999999999</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.05</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3125</v>
+        <v>0.33875</v>
       </c>
       <c r="N8" t="n">
-        <v>10.21625</v>
+        <v>10.61375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.19</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4037500000000001</v>
+        <v>0.40375</v>
       </c>
       <c r="N9" t="n">
         <v>11.2075</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3062</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>888</v>
+      </c>
+      <c r="D75" t="n">
+        <v>849</v>
+      </c>
+      <c r="E75" t="n">
+        <v>39</v>
+      </c>
+      <c r="F75" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-134</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-15.10%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>17</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-117</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-109</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.02624999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>5.976249999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.388888888888889</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>2.717948717948718</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.5499999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1447368421052631</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
